--- a/out/Attention-MambaAMT_repeat_5_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.034846904977811</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.967222099549091</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001099187127304031</v>
+        <v>-0.0001676808107870165</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1262754890924216</v>
+        <v>-0.1926330455260462</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1264823519483287</v>
+        <v>-0.192941863446285</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3485888039987721</v>
+        <v>0.507496902937696</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5713650737966635</v>
+        <v>0.8230263550666476</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02483687909662885</v>
+        <v>0.03615901119606519</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.967222099549091</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2718904123060084</v>
+        <v>0.3870334671199133</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04355555180607714</v>
+        <v>0.06341071381903395</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3341562749812875</v>
+        <v>0.4776837432632751</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05291453978800207</v>
+        <v>0.07703621675771917</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3964262825660713</v>
+        <v>0.568340053545339</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01400267802519771</v>
+        <v>0.02038571311170338</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.034846904977811</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3714489166023573</v>
+        <v>0.5319766141714982</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007777834716117005</v>
+        <v>0.01132585934794351</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3729901280227078</v>
+        <v>0.5342226929083159</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01634440367404211</v>
+        <v>0.02379623135082797</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3979111152093439</v>
+        <v>0.5705040773620281</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006418534503364094</v>
+        <v>0.009345699453332234</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3943890356806293</v>
+        <v>0.5653789557053144</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004569527978479704</v>
+        <v>0.006654974556904275</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3971068806531336</v>
+        <v>0.569338097650578</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001795563729669258</v>
+        <v>0.002615730013771998</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3961249198738397</v>
+        <v>0.5679107585939877</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001016956929727278</v>
+        <v>0.001482463706164138</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.396362220801051</v>
+        <v>0.5682586126151178</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003837162153556499</v>
+        <v>0.0005622203384192717</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3961130544902314</v>
+        <v>0.5678978578329117</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001777594336070846</v>
+        <v>0.0002603314668632975</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3960834054359899</v>
+        <v>0.567856998660794</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.200799943137988e-05</v>
+        <v>9.268636061683091e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3960295086922115</v>
+        <v>0.5677807154560089</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.455641581801909e-05</v>
+        <v>2.361914509954013e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3959970270384962</v>
+        <v>0.5677356516698914</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.016700784839047e-06</v>
+        <v>9.309572549770066e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3959920114010135</v>
+        <v>0.5677306293306302</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.369014529177619e-07</v>
+        <v>2.705352179376644e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3959877752319395</v>
+        <v>0.5677267567027733</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>5.776969076452056e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3959847913528339</v>
+        <v>0.5677246885082696</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-2.504786695239595e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3959793476078275</v>
+        <v>0.5677190968482613</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>-4.413072433009741e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3959733548743972</v>
+        <v>0.5677127728542534</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3959679870858188</v>
+        <v>0.5677074050656751</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3959680238343105</v>
+        <v>0.5677074418141668</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.395968134079786</v>
+        <v>0.5677075520596423</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.4348469049778107</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3959682075767696</v>
+        <v>0.5677076255566259</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3959683913192288</v>
+        <v>0.567707809299085</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3959699347558853</v>
+        <v>0.5677093527357415</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3959714046955584</v>
+        <v>0.5677108226754146</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3959726541442803</v>
+        <v>0.5677120721241367</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3959740138384777</v>
+        <v>0.5677134318183339</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3959718089289684</v>
+        <v>0.5677112269088246</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3959714046955584</v>
+        <v>0.5677108226754146</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3959705594802464</v>
+        <v>0.5677099774601027</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3959711107076236</v>
+        <v>0.56771052868748</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3959707799711972</v>
+        <v>0.5677101979510535</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3959704859832628</v>
+        <v>0.567709903963119</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3959705594802464</v>
+        <v>0.5677099774601027</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3959701184983445</v>
+        <v>0.5677095364782007</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3959700082528689</v>
+        <v>0.5677094262327251</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3959699715043772</v>
+        <v>0.5677093894842334</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3959701184983445</v>
+        <v>0.5677095364782007</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3959696407679508</v>
+        <v>0.5677090587478071</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.4348469049778107</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3959705962287381</v>
+        <v>0.5677100142085943</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3959705594802464</v>
+        <v>0.5677099774601027</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.39597022874382</v>
+        <v>0.5677096467236762</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3959706697257219</v>
+        <v>0.5677100877055782</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.034846904977811</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3959700450013608</v>
+        <v>0.5677094629812171</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3959698612589017</v>
+        <v>0.5677092792387579</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3959694570254916</v>
+        <v>0.5677088750053478</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3959686118101797</v>
+        <v>0.5677080297900359</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.395968575061688</v>
+        <v>0.5677079930415442</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3959687220556552</v>
+        <v>0.5677081400355115</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3959686485586716</v>
+        <v>0.5677080665385278</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3959687220556552</v>
+        <v>0.5677081400355115</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3959687588041471</v>
+        <v>0.5677081767840034</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3959686485586716</v>
+        <v>0.5677080665385278</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3959690895405735</v>
+        <v>0.5677085075204298</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.395968979295098</v>
+        <v>0.5677083972749543</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3959689425466061</v>
+        <v>0.5677083605264623</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3959688690496224</v>
+        <v>0.5677082870294787</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3959688323011307</v>
+        <v>0.567708250280987</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3959686118101797</v>
+        <v>0.5677080297900359</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3959685383131961</v>
+        <v>0.5677079562930523</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3959684648162124</v>
+        <v>0.5677078827960687</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3959685015647044</v>
+        <v>0.5677079195445606</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3959683913192288</v>
+        <v>0.567707809299085</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3959685015647044</v>
+        <v>0.5677079195445606</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3959687955526388</v>
+        <v>0.5677082135324951</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_5_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.967222099549091</v>
+        <v>-0.3137207519070788</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.3137207519070788</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.967222099549091</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.034846904977811</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001099187127304031</v>
+        <v>-0.000110581225528731</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1262754890924216</v>
+        <v>-0.127036589050452</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.126385407805152</v>
+        <v>-0.1271471702759807</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1264823519483287</v>
+        <v>-0.1272446694293878</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3485888039987721</v>
+        <v>0.350584751135203</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.3137207519070788</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5713650737966635</v>
+        <v>0.5745979684011717</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02483687909662885</v>
+        <v>0.02497905332477303</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.967222099549091</v>
+        <v>-0.3137207519070788</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2718904123060084</v>
+        <v>0.2734090208287486</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04355555180607714</v>
+        <v>0.04380474864079241</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.3137207519070788</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3341562749812875</v>
+        <v>0.3360313124378822</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05291453978800207</v>
+        <v>0.05321759629880223</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3964262825660713</v>
+        <v>0.3986579558345441</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01400267802519771</v>
+        <v>0.01408287437109611</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.034846904977811</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3714489166023573</v>
+        <v>0.373537539128904</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007777834716117005</v>
+        <v>0.007822593169749809</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3729901280227078</v>
+        <v>0.3750876057263762</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01634440367404211</v>
+        <v>0.01643839901901397</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3979111152093439</v>
+        <v>0.4001507287822722</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006418534503364094</v>
+        <v>0.006454866712093528</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3943890356806293</v>
+        <v>0.3966087562697981</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004569527978479704</v>
+        <v>0.004595402005507303</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3971068806531336</v>
+        <v>0.3993420019491604</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001795563729669258</v>
+        <v>0.001805068968061178</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3961249198738397</v>
+        <v>0.398354516275103</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001016956929727278</v>
+        <v>0.001023122582395316</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.396362220801051</v>
+        <v>0.3985932790480289</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003837162153556499</v>
+        <v>0.0003860649538170134</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3961130544902314</v>
+        <v>0.3983426396325212</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001777594336070846</v>
+        <v>0.0001788603940505008</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3960834054359899</v>
+        <v>0.3983128420900008</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3960295086922115</v>
+        <v>0.398258651358288</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.455641581801909e-05</v>
+        <v>1.503340156967809e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3959970270384962</v>
+        <v>0.3982258382235042</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3959920114010135</v>
+        <v>0.3982208225860214</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3959877752319395</v>
+        <v>0.3982165864169474</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3959847913528339</v>
+        <v>0.3982136025378418</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3959793476078275</v>
+        <v>0.3982081587928354</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3959733548743972</v>
+        <v>0.3982021660594051</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3959679870858188</v>
+        <v>0.3981967982708267</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3959680238343105</v>
+        <v>0.3981968350193184</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.395968134079786</v>
+        <v>0.3981969452647939</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3959682075767696</v>
+        <v>0.3981970187617775</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3959683913192288</v>
+        <v>0.3981972025042367</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3959699347558853</v>
+        <v>0.3981987459408932</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3959714046955584</v>
+        <v>0.3982002158805663</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.967222099549091</v>
+        <v>-0.3137207519070788</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3959726541442803</v>
+        <v>0.3982014653292883</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.3137207519070788</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3959740138384777</v>
+        <v>0.3982028250234856</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3959718089289684</v>
+        <v>0.3982006201139763</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.034846904977811</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3959714046955584</v>
+        <v>0.3982002158805663</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3959705594802464</v>
+        <v>0.3981993706652543</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3959711107076236</v>
+        <v>0.3981999218926316</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3959707799711972</v>
+        <v>0.3981995911562052</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3959704859832628</v>
+        <v>0.3981992971682707</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070789</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3959705594802464</v>
+        <v>0.3981993706652543</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.967222099549091</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3959701184983445</v>
+        <v>0.3981989296833524</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.3137207519070789</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3959700082528689</v>
+        <v>0.3981988194378768</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.3137207519070788</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3959699715043772</v>
+        <v>0.3981987826893851</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.967222099549091</v>
+        <v>-0.3137207519070788</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3959701184983445</v>
+        <v>0.3981989296833524</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.4348469049778107</v>
+        <v>-0.3137207519070788</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3959696407679508</v>
+        <v>0.3981984519529587</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.4348469049778107</v>
+        <v>0.463895020556213</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3959705962287381</v>
+        <v>0.398199407413746</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3959705594802464</v>
+        <v>0.3981993706652543</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.39597022874382</v>
+        <v>0.3981990399288279</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.034846904977811</v>
+        <v>0.6638950205562131</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3959706697257219</v>
+        <v>0.3981994809107299</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.034846904977811</v>
+        <v>-0.1137207519070788</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3959700450013608</v>
+        <v>0.3981988561863687</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.091336524370371</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3959698612589017</v>
+        <v>0.3981986724439096</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3959694570254916</v>
+        <v>0.3981982682104995</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3959686118101797</v>
+        <v>0.3981974229951876</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.395968575061688</v>
+        <v>0.3981973862466959</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3959687220556552</v>
+        <v>0.3981975332406631</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3959686485586716</v>
+        <v>0.3981974597436795</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3959687220556552</v>
+        <v>0.3981975332406631</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3959687588041471</v>
+        <v>0.3981975699891551</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3959686485586716</v>
+        <v>0.3981974597436795</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3959690895405735</v>
+        <v>0.3981979007255815</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.395968979295098</v>
+        <v>0.3981977904801059</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3959689425466061</v>
+        <v>0.398197753731614</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3959688690496224</v>
+        <v>0.3981976802346304</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3959688323011307</v>
+        <v>0.3981976434861387</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3959686118101797</v>
+        <v>0.3981974229951876</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3959685383131961</v>
+        <v>0.398197349498204</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3959684648162124</v>
+        <v>0.3981972760012203</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3959685015647044</v>
+        <v>0.3981973127497123</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3959683913192288</v>
+        <v>0.3981972025042367</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3959685015647044</v>
+        <v>0.3981973127497123</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-2.967222099549091</v>
+        <v>-1.868952296833663</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3959687955526388</v>
+        <v>0.3981976067376468</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_5_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.04774624109268188</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.03028561547398567</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.3700000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.02036838978528976</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.1137207519070789</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.0008146539330482483</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3137207519070788</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.007180884480476379</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3137207519070788</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.02729019522666931</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.02758656442165375</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.16</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0316280722618103</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.02908206731081009</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.04025113955140114</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.04156754165887833</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0317525789141655</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.04151100665330887</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.03387750312685966</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3137207519070789</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.008461788296699524</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3137207519070789</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.03584574535489082</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3137207519070789</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.03901678323745728</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.04457436501979828</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.463895020556213</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.04736778885126114</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.05185862258076668</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.04515234753489494</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.05546361207962036</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.05081312358379364</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.05137974768877029</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.04925358295440674</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.05387275665998459</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.463895020556213</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.05736072733998299</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.463895020556213</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.05600900948047638</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.463895020556213</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0502297505736351</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.05638138949871063</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01419222727417946</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.04825885593891144</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.04895241558551788</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.04480612277984619</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.04337404295802116</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.16</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.04941808432340622</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.04163223877549171</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.463895020556213</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.04602507874369621</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.463895020556213</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.04626079648733139</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.463895020556213</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01593492552638054</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.03411680832505226</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01586995646357536</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.02008932083845139</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.02581863477826118</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.000110581225528731</v>
+        <v>-7.719068296707701e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.127036589050452</v>
+        <v>-0.08867726889193431</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.00834386795759201</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.00239911675453186</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.005131028592586517</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01625506207346916</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01060666888952255</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01982508972287178</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01033037155866623</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.02176938205957413</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.006418317556381226</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01906881108880043</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.0177915021777153</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01983675360679626</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.02030261605978012</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1271471702759807</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01284196972846985</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1272446694293878</v>
+        <v>-0.08882259802308166</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.350584751135203</v>
+        <v>0.2450100850180599</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.001655057072639465</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3137207519070788</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5745979684011717</v>
+        <v>0.4016685148271203</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02497905332477303</v>
+        <v>0.01745691711621853</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0006955713033676147</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3137207519070788</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2734090208287486</v>
+        <v>0.191178799990556</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04380474864079241</v>
+        <v>0.03061348468161163</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.005412615835666656</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3137207519070788</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3360313124378822</v>
+        <v>0.2349432102014082</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05321759629880223</v>
+        <v>0.03719176846430827</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01530494540929794</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3986579558345441</v>
+        <v>0.2787107170440257</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01408287437109611</v>
+        <v>0.009841275378308329</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01384075358510017</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.373537539128904</v>
+        <v>0.2611541543437242</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007822593169749809</v>
+        <v>0.005465436902612457</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.02217122167348862</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3750876057263762</v>
+        <v>0.2622359371537592</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01643839901901397</v>
+        <v>0.01148623516005559</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01309015974402428</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4001507287822722</v>
+        <v>0.2797504684094372</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006454866712093528</v>
+        <v>0.004509882471444446</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.007040530443191528</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3966087562697981</v>
+        <v>0.2772734336275656</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004595402005507303</v>
+        <v>0.00321027909196311</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.007380463182926178</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3993420019491604</v>
+        <v>0.2791822281331267</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001805068968061178</v>
+        <v>0.001260554597324094</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.009633906185626984</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.398354516275103</v>
+        <v>0.2784905558508476</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001023122582395316</v>
+        <v>0.0007132985358264126</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01230138912796974</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.16</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3985932790480289</v>
+        <v>0.27865586087661</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003860649538170134</v>
+        <v>0.0002686280307488412</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.01512421667575836</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.6638950205562131</v>
+        <v>0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3983426396325212</v>
+        <v>0.2784792441804321</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001788603940505008</v>
+        <v>0.000122711411436276</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01441366598010063</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.463895020556213</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3983128420900008</v>
+        <v>0.2784569460431346</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.200799943137988e-05</v>
+        <v>4.182486707253051e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.01377962902188301</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.463895020556213</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.398258651358288</v>
+        <v>0.278417483246295</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.503340156967809e-05</v>
+        <v>8.832586798111064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01866833493113518</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.463895020556213</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3982258382235042</v>
+        <v>0.2783929482025178</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.016700784839047e-06</v>
+        <v>2.154786274885033e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.03268641233444214</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.463895020556213</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3982208225860214</v>
+        <v>0.278387937032887</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.369014529177619e-07</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.02431167289614677</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.463895020556213</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3982165864169474</v>
+        <v>0.2783834827390828</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.02080550044775009</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.463895020556213</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3982136025378418</v>
+        <v>0.2783799486418308</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.02097052708268166</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.463895020556213</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3982081587928354</v>
+        <v>0.2783746528118267</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.02390860766172409</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.463895020556213</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3982021660594051</v>
+        <v>0.278368990814823</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01665638387203217</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.463895020556213</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3981967982708267</v>
+        <v>0.2783688070723638</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.03688453882932663</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.463895020556213</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3981968350193184</v>
+        <v>0.2783688438208555</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01933375373482704</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3981969452647939</v>
+        <v>0.2783689540663311</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.02865497767925262</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.463895020556213</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3981970187617775</v>
+        <v>0.2783690275633147</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01976092532277107</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3981972025042367</v>
+        <v>0.2783692113057738</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.03609796613454819</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3981987459408932</v>
+        <v>0.2783707547424303</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01192358136177063</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3137207519070789</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3982002158805663</v>
+        <v>0.2783722246821034</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.003490887582302094</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3137207519070788</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3982014653292883</v>
+        <v>0.2783734741308254</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.07517313957214355</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3137207519070788</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3982028250234856</v>
+        <v>0.2783748338250227</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.009942851960659027</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3982006201139763</v>
+        <v>0.2783726289155134</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.03135587647557259</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3982002158805663</v>
+        <v>0.2783722246821034</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01328477263450623</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3981993706652543</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.0140986330807209</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3981999218926316</v>
+        <v>0.2783719306941687</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.007612451910972595</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3981995911562052</v>
+        <v>0.2783715999577422</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.008105657994747162</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3981992971682707</v>
+        <v>0.2783713059698078</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.01216325163841248</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1137207519070789</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3981993706652543</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.0003597736358642578</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3137207519070789</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3981989296833524</v>
+        <v>0.2783709384848895</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.005791850388050079</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3137207519070789</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3981988194378768</v>
+        <v>0.2783708282394139</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.001302152872085571</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3137207519070788</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3981987826893851</v>
+        <v>0.2783707914909222</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.0007977187633514404</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3137207519070788</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3981989296833524</v>
+        <v>0.2783709384848895</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.008983127772808075</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3137207519070788</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3981984519529587</v>
+        <v>0.2783704607544958</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.02109265699982643</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.463895020556213</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.398199407413746</v>
+        <v>0.2783714162152831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.002135090529918671</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3981993706652543</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.002146191895008087</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3981990399288279</v>
+        <v>0.278371048730365</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.006853938102722168</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.6638950205562131</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3981994809107299</v>
+        <v>0.2783714897122669</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.00241515040397644</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1137207519070788</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3981988561863687</v>
+        <v>0.2783708649879058</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.002510786056518555</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.091336524370371</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3981986724439096</v>
+        <v>0.2783706812454467</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.003489203751087189</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3981982682104995</v>
+        <v>0.2783702770120366</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.03023349493741989</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3981974229951876</v>
+        <v>0.2783694317967247</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.02045808732509613</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3981973862466959</v>
+        <v>0.278369395048233</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.001197315752506256</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3981975332406631</v>
+        <v>0.2783695420422002</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.02455594390630722</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3981974597436795</v>
+        <v>0.2783694685452166</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01392468810081482</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3981975332406631</v>
+        <v>0.2783695420422002</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.025532066822052</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3981975699891551</v>
+        <v>0.2783695787906921</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01573210209608078</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3981974597436795</v>
+        <v>0.2783694685452166</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.01503341645002365</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3981979007255815</v>
+        <v>0.2783699095271185</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.0108024850487709</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3981977904801059</v>
+        <v>0.278369799281643</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.006949126720428467</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.398197753731614</v>
+        <v>0.2783697625331511</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.006209172308444977</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3981976802346304</v>
+        <v>0.2783696890361674</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.01128339767456055</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3981976434861387</v>
+        <v>0.2783696522876757</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01140334457159042</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3981974229951876</v>
+        <v>0.2783694317967247</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02211318165063858</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.398197349498204</v>
+        <v>0.2783693582997411</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.00626751035451889</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3981972760012203</v>
+        <v>0.2783692848027574</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01532527059316635</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3981973127497123</v>
+        <v>0.2783693215512494</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.02034708857536316</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3981972025042367</v>
+        <v>0.2783692113057738</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.03000177443027496</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.3999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3981973127497123</v>
+        <v>0.2783693215512494</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.03049670904874802</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.868952296833663</v>
+        <v>-0.3999999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3981976067376468</v>
+        <v>0.2783696155391838</v>
       </c>
     </row>
   </sheetData>
